--- a/lab2/ELEC475_2025_Lab2_Self_Assessment.xlsx
+++ b/lab2/ELEC475_2025_Lab2_Self_Assessment.xlsx
@@ -1,65 +1,175 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aytu_\Desktop\elec475_lab\lab2_submission\20354469\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_1A4D0FAED62D31348B4FBFE66E44FF376835239D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="2355" yWindow="3315" windowWidth="24330" windowHeight="14640" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="760" yWindow="760" windowWidth="19200" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="162913" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
+  <si>
+    <t>ELEC 475 Lab 2 Post-Lab Self-Assessment</t>
+  </si>
+  <si>
+    <t>Name(s):</t>
+  </si>
+  <si>
+    <t>Aytu Tuna</t>
+  </si>
+  <si>
+    <t>Student Number(s):</t>
+  </si>
+  <si>
+    <t>20354469</t>
+  </si>
+  <si>
+    <t>Item</t>
+  </si>
+  <si>
+    <t>Full Marks</t>
+  </si>
+  <si>
+    <t>Half Marks</t>
+  </si>
+  <si>
+    <t>No Marks</t>
+  </si>
+  <si>
+    <t>Max</t>
+  </si>
+  <si>
+    <t>Mark</t>
+  </si>
+  <si>
+    <t>Full AlexNet Architecture &amp; Zoo Baseline</t>
+  </si>
+  <si>
+    <t>Works perfectly, and output is correct.</t>
+  </si>
+  <si>
+    <t>Works somewhat, and output is mostly correct.</t>
+  </si>
+  <si>
+    <t>Doesn't work.</t>
+  </si>
+  <si>
+    <t>Empirical
+Normalization &amp;
+Extended Ablation
+Study</t>
+  </si>
+  <si>
+    <t>Master ablation table complete and correct.</t>
+  </si>
+  <si>
+    <t>Master ablation table somewhat complete and somewhat correct.</t>
+  </si>
+  <si>
+    <t>Master ablation table incomplete and/or incorrect.</t>
+  </si>
+  <si>
+    <t>PyTorch Data Augmentation</t>
+  </si>
+  <si>
+    <t>All augmentations implemented and work correctly.</t>
+  </si>
+  <si>
+    <t>Some augmentations implemented and work correctly.</t>
+  </si>
+  <si>
+    <t>Augmentations not implemented and/or incorrect.</t>
+  </si>
+  <si>
+    <t>Technical Analysis &amp;
+Discussion</t>
+  </si>
+  <si>
+    <t>Correct and complete desciption and discussion of results.</t>
+  </si>
+  <si>
+    <t>Somewhat correct and somewhat complete desciption and discussion of results.</t>
+  </si>
+  <si>
+    <t>Incorrect and/or incomplete description and discussion of results</t>
+  </si>
+  <si>
+    <t>Submission and Format</t>
+  </si>
+  <si>
+    <t>Report includes all sections specified with correct level of detail, and is formatted as specified. Submission format as specified.</t>
+  </si>
+  <si>
+    <t>Report contains some of the sections and details as specified, and some of the formatting is correct. Submission format has some unspecified elements.</t>
+  </si>
+  <si>
+    <t>Report is missing significant sections or details, and the formatting is not as specified. Submission format is not as specified.</t>
+  </si>
+  <si>
+    <t>TOTAL:</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="4">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <b val="1"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <u val="single"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <b val="1"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <u val="single"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.1499984740745262"/>
+        <fgColor theme="0" tint="-0.14999847407452621"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -96,130 +206,72 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="19">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -485,281 +537,214 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F18"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="30.7109375" customWidth="1" min="2" max="4"/>
+    <col min="1" max="1" width="30" customWidth="1"/>
+    <col min="2" max="4" width="30.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="17" t="inlineStr">
-        <is>
-          <t>ELEC 475 Lab 2 Post-Lab Self-Assessment</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="13" t="inlineStr">
-        <is>
-          <t>Name(s):</t>
-        </is>
-      </c>
-      <c r="B2" s="12" t="inlineStr">
-        <is>
-          <t>Aytu Tuna</t>
-        </is>
-      </c>
-      <c r="C2" s="12" t="n"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="14" t="inlineStr">
-        <is>
-          <t>Student Number(s):</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>20354469</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="8" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="B4" s="8" t="inlineStr">
-        <is>
-          <t>Full Marks</t>
-        </is>
-      </c>
-      <c r="C4" s="8" t="inlineStr">
-        <is>
-          <t>Half Marks</t>
-        </is>
-      </c>
-      <c r="D4" s="8" t="inlineStr">
-        <is>
-          <t>No Marks</t>
-        </is>
-      </c>
-      <c r="E4" s="8" t="inlineStr">
-        <is>
-          <t>Max</t>
-        </is>
-      </c>
-      <c r="F4" s="8" t="inlineStr">
-        <is>
-          <t>Mark</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="15" t="inlineStr">
-        <is>
-          <t>Full AlexNet Architecture &amp; Zoo Baseline</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>Works perfectly, and output is correct.</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>Works somewhat, and output is mostly correct.</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>Doesn't work.</t>
-        </is>
-      </c>
-      <c r="E5" s="7" t="n">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A2" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="F5" s="5" t="n">
+      <c r="B2" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="12"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A3" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A4" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" s="7">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" ht="60" customHeight="1">
-      <c r="A6" s="16" t="inlineStr">
-        <is>
-          <t>Empirical
-Normalization &amp;
-Extended Ablation
-Study</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>Master ablation table complete and correct.</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>Master ablation table somewhat complete and somewhat correct.</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>Master ablation table incomplete and/or incorrect.</t>
-        </is>
-      </c>
-      <c r="E6" s="7" t="n">
+      <c r="F5" s="5">
         <v>1</v>
       </c>
-      <c r="F6" s="5" t="n">
+    </row>
+    <row r="6" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" s="7">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" ht="45" customHeight="1">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>PyTorch Data Augmentation</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>All augmentations implemented and work correctly.</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>Some augmentations implemented and work correctly.</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>Augmentations not implemented and/or incorrect.</t>
-        </is>
-      </c>
-      <c r="E7" s="7" t="n">
+      <c r="F6" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E7" s="7">
         <v>0.5</v>
       </c>
-      <c r="F7" s="5" t="n">
+      <c r="F7" s="5">
         <v>0.5</v>
       </c>
     </row>
-    <row r="8" ht="45" customHeight="1">
-      <c r="A8" s="15" t="inlineStr">
-        <is>
-          <t>Technical Analysis &amp;
-Discussion</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>Correct and complete desciption and discussion of results.</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>Somewhat correct and somewhat complete desciption and discussion of results.</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>Incorrect and/or incomplete description and discussion of results</t>
-        </is>
-      </c>
-      <c r="E8" s="7" t="n">
+    <row r="8" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E8" s="7">
         <v>1</v>
       </c>
-      <c r="F8" s="5" t="n">
+      <c r="F8" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="9" ht="75" customHeight="1">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>Submission and Format</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>Report includes all sections specified with correct level of detail, and is formatted as specified. Submission format as specified.</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>Report contains some of the sections and details as specified, and some of the formatting is correct. Submission format has some unspecified elements.</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>Report is missing significant sections or details, and the formatting is not as specified. Submission format is not as specified.</t>
-        </is>
-      </c>
-      <c r="E9" s="7" t="n">
+    <row r="9" spans="1:6" ht="75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="E9" s="7">
         <v>0.5</v>
       </c>
-      <c r="F9" s="5" t="n">
+      <c r="F9" s="5">
         <v>0.5</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="2" t="n"/>
-      <c r="B10" s="4" t="n"/>
-      <c r="C10" s="4" t="n"/>
-      <c r="D10" s="10" t="inlineStr">
-        <is>
-          <t>TOTAL:</t>
-        </is>
-      </c>
-      <c r="E10" s="11" t="n">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A10" s="2"/>
+      <c r="B10" s="4"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="E10" s="11">
         <v>4</v>
       </c>
-      <c r="F10" s="2" t="n">
+      <c r="F10" s="2">
         <v>4</v>
       </c>
     </row>
-    <row r="11">
-      <c r="B11" s="4" t="n"/>
-      <c r="C11" s="4" t="n"/>
-      <c r="D11" s="4" t="n"/>
-    </row>
-    <row r="12">
-      <c r="B12" s="4" t="n"/>
-      <c r="C12" s="4" t="n"/>
-      <c r="D12" s="4" t="n"/>
-    </row>
-    <row r="13">
-      <c r="B13" s="4" t="n"/>
-      <c r="C13" s="4" t="n"/>
-      <c r="D13" s="4" t="n"/>
-    </row>
-    <row r="14">
-      <c r="B14" s="3" t="n"/>
-      <c r="C14" s="3" t="n"/>
-      <c r="D14" s="3" t="n"/>
-    </row>
-    <row r="15">
-      <c r="B15" s="3" t="n"/>
-      <c r="C15" s="3" t="n"/>
-      <c r="D15" s="3" t="n"/>
-    </row>
-    <row r="16">
-      <c r="B16" s="3" t="n"/>
-      <c r="C16" s="3" t="n"/>
-      <c r="D16" s="3" t="n"/>
-    </row>
-    <row r="17">
-      <c r="B17" s="1" t="n"/>
-      <c r="C17" s="1" t="n"/>
-      <c r="D17" s="1" t="n"/>
-    </row>
-    <row r="18">
-      <c r="B18" s="1" t="n"/>
-      <c r="C18" s="1" t="n"/>
-      <c r="D18" s="1" t="n"/>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B11" s="4"/>
+      <c r="C11" s="4"/>
+      <c r="D11" s="4"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B12" s="4"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="4"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B13" s="4"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="4"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B14" s="3"/>
+      <c r="C14" s="3"/>
+      <c r="D14" s="3"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B15" s="3"/>
+      <c r="C15" s="3"/>
+      <c r="D15" s="3"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B16" s="3"/>
+      <c r="C16" s="3"/>
+      <c r="D16" s="3"/>
+    </row>
+    <row r="17" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B17" s="1"/>
+      <c r="C17" s="1"/>
+      <c r="D17" s="1"/>
+    </row>
+    <row r="18" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B18" s="1"/>
+      <c r="C18" s="1"/>
+      <c r="D18" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="1">
